--- a/plots/countries/sectors/European Union-sectors.xlsx
+++ b/plots/countries/sectors/European Union-sectors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">Author</t>
   </si>
@@ -30,13 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2025). Tidy GHG Inventories (1.0) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14945466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See also</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -443,14 +437,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -464,79 +450,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
       <c r="D2" t="n">
         <v>1990</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>487.559149994823</v>
+        <v>487.78337171747</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>1990</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>735.328683479373</v>
+        <v>735.34392009489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>1990</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>164.953406195342</v>
@@ -544,179 +530,179 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>1990</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>720.684462147886</v>
+        <v>721.827848879459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>1990</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>1442.03893678453</v>
+        <v>1442.2831564725</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>1990</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>674.121153781592</v>
+        <v>675.935877769744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
         <v>1990</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>450.241838752362</v>
+        <v>450.146045519006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>1990</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>-254.760336772166</v>
+        <v>-258.202356037772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>1990</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>185.406943102083</v>
+        <v>185.570648266128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>1991</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>459.609820678172</v>
+        <v>459.899890663091</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>1991</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>766.013395870409</v>
+        <v>766.012422610258</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
         <v>1991</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
         <v>151.688793335715</v>
@@ -724,179 +710,179 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
         <v>1991</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>677.842091149997</v>
+        <v>679.125184533095</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
         <v>1991</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>1409.51102720086</v>
+        <v>1409.77260165066</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
         <v>1991</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>682.75204565301</v>
+        <v>684.540983270176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>1991</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>418.451433312552</v>
+        <v>418.52760313307</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
         <v>1991</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>-351.176456445037</v>
+        <v>-356.241752382451</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>1991</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>188.687357111752</v>
+        <v>188.859007012889</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>1992</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>439.057740686407</v>
+        <v>439.352996445015</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
         <v>1992</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>714.465666760384</v>
+        <v>714.469879601887</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
         <v>1992</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>147.610132393333</v>
@@ -904,179 +890,179 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="n">
         <v>1992</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>638.890136369594</v>
+        <v>640.213095470336</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>1992</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>1362.90749406716</v>
+        <v>1363.19104868969</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
         <v>1992</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>704.611393959495</v>
+        <v>706.36082320087</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>1992</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>405.689666183626</v>
+        <v>405.502899354604</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
         <v>1992</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>-318.619473662248</v>
+        <v>-325.451849148455</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>1992</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>190.402867238205</v>
+        <v>190.583353002783</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
         <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
       </c>
       <c r="D29" t="n">
         <v>1993</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>427.170285408063</v>
+        <v>427.459300208373</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
         <v>1993</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>725.472972455622</v>
+        <v>725.460860332773</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
         <v>1993</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>146.920432040919</v>
@@ -1084,179 +1070,179 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D32" t="n">
         <v>1993</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>618.820634903359</v>
+        <v>620.237088925102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
         <v>1993</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>1311.49705242656</v>
+        <v>1311.82807279145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D34" t="n">
         <v>1993</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>708.038230308497</v>
+        <v>709.78436091419</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" t="n">
         <v>1993</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>395.644327974403</v>
+        <v>395.526095468799</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
         <v>1993</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>-340.704401708179</v>
+        <v>-347.007602774162</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>1993</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>190.3679030462</v>
+        <v>190.55889717658</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
         <v>14</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" t="s">
-        <v>16</v>
       </c>
       <c r="D38" t="n">
         <v>1994</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>421.927934333867</v>
+        <v>422.230207313558</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" t="n">
         <v>1994</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>680.932190812287</v>
+        <v>680.914281994587</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D40" t="n">
         <v>1994</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F40" t="n">
         <v>142.70355064642</v>
@@ -1264,179 +1250,179 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" t="n">
         <v>1994</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>616.638956769905</v>
+        <v>617.993996088603</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>1994</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>1318.02534588825</v>
+        <v>1318.43403763306</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
         <v>1994</v>
       </c>
       <c r="E43" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>713.362959269494</v>
+        <v>715.049023466294</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
         <v>1994</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>418.982862232884</v>
+        <v>419.032655681113</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="n">
         <v>1994</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>-338.527538487017</v>
+        <v>-344.831112288824</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
         <v>1994</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>189.342691520152</v>
+        <v>189.527341881755</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
         <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>16</v>
       </c>
       <c r="D47" t="n">
         <v>1995</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>422.021625129102</v>
+        <v>422.351880777335</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D48" t="n">
         <v>1995</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>687.542961264636</v>
+        <v>687.546640296945</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
         <v>1995</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F49" t="n">
         <v>141.348989792379</v>
@@ -1444,179 +1430,179 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
         <v>1995</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>637.647192998615</v>
+        <v>639.244149234641</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>1995</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>1318.67108016261</v>
+        <v>1319.08348348771</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="n">
         <v>1995</v>
       </c>
       <c r="E52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>726.276949834294</v>
+        <v>727.939538331425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" t="n">
         <v>1995</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>429.983704739847</v>
+        <v>430.667186273616</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D54" t="n">
         <v>1995</v>
       </c>
       <c r="E54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>-366.064211769462</v>
+        <v>-372.284351544039</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>1995</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>188.881082981164</v>
+        <v>189.070547547451</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
         <v>14</v>
-      </c>
-      <c r="B56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" t="s">
-        <v>16</v>
       </c>
       <c r="D56" t="n">
         <v>1996</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>422.757979779534</v>
+        <v>423.069604464441</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
         <v>1996</v>
       </c>
       <c r="E57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>741.75307255508</v>
+        <v>741.709355525079</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="n">
         <v>1996</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F58" t="n">
         <v>137.350371427759</v>
@@ -1624,179 +1610,179 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
         <v>1996</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>629.568365159492</v>
+        <v>631.081846030062</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D60" t="n">
         <v>1996</v>
       </c>
       <c r="E60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>1347.41810085237</v>
+        <v>1347.82187630175</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" t="n">
         <v>1996</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>748.411754480752</v>
+        <v>750.135339698572</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
         <v>1996</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>429.211983295889</v>
+        <v>430.002551147515</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
         <v>1996</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>-383.423478381303</v>
+        <v>-388.611394097803</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
         <v>1996</v>
       </c>
       <c r="E64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>187.303256693509</v>
+        <v>187.497796921901</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
       </c>
       <c r="D65" t="n">
         <v>1997</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>420.260819390133</v>
+        <v>420.525247140324</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" t="n">
         <v>1997</v>
       </c>
       <c r="E66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F66" t="n">
-        <v>700.668252873832</v>
+        <v>700.625355647452</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D67" t="n">
         <v>1997</v>
       </c>
       <c r="E67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F67" t="n">
         <v>135.788567458484</v>
@@ -1804,179 +1790,179 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D68" t="n">
         <v>1997</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>620.936818156246</v>
+        <v>622.531762925531</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
         <v>1997</v>
       </c>
       <c r="E69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>1312.62832412349</v>
+        <v>1313.04225601282</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>1997</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F70" t="n">
-        <v>758.118497388158</v>
+        <v>759.817839321571</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
         <v>1997</v>
       </c>
       <c r="E71" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>433.956378789486</v>
+        <v>434.895152739708</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D72" t="n">
         <v>1997</v>
       </c>
       <c r="E72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>-371.661691283742</v>
+        <v>-377.412440750172</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>1997</v>
       </c>
       <c r="E73" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>184.420518814504</v>
+        <v>184.619635542285</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
         <v>14</v>
-      </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" t="s">
-        <v>16</v>
       </c>
       <c r="D74" t="n">
         <v>1998</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>417.61222636215</v>
+        <v>417.87323981503</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D75" t="n">
         <v>1998</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="n">
-        <v>684.856101675433</v>
+        <v>684.785048947833</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D76" t="n">
         <v>1998</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
         <v>127.936789967835</v>
@@ -1984,179 +1970,179 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
         <v>1998</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>596.16592507173</v>
+        <v>597.813192138818</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>1998</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F78" t="n">
-        <v>1315.74593504796</v>
+        <v>1316.18098709804</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" t="n">
         <v>1998</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F79" t="n">
-        <v>787.177114422527</v>
+        <v>788.94457878624</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D80" t="n">
         <v>1998</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>417.086903470714</v>
+        <v>417.914536331463</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
         <v>1998</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>-370.883804758836</v>
+        <v>-376.854973742779</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D82" t="n">
         <v>1998</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>181.139182617099</v>
+        <v>181.343121493076</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>14</v>
-      </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
       </c>
       <c r="D83" t="n">
         <v>1999</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>414.398045354285</v>
+        <v>414.663641575925</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D84" t="n">
         <v>1999</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>671.488433522662</v>
+        <v>671.350099049741</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D85" t="n">
         <v>1999</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
         <v>126.167009136869</v>
@@ -2164,179 +2150,179 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D86" t="n">
         <v>1999</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>581.721570904506</v>
+        <v>583.391586721364</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
         <v>1999</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
-        <v>1278.33773978605</v>
+        <v>1278.8482174217</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>1999</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>803.771500660534</v>
+        <v>805.490111883857</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D89" t="n">
         <v>1999</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>398.402286120077</v>
+        <v>399.034907386146</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>1999</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>-378.267678628599</v>
+        <v>-383.796913832862</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="n">
         <v>1999</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>178.180626026171</v>
+        <v>178.388931890196</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
         <v>14</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
       </c>
       <c r="D92" t="n">
         <v>2000</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>410.936394437902</v>
+        <v>411.184144851338</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D93" t="n">
         <v>2000</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>646.43058416677</v>
+        <v>646.123834906343</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D94" t="n">
         <v>2000</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
         <v>110.648319148704</v>
@@ -2344,179 +2330,179 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D95" t="n">
         <v>2000</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>580.067144293806</v>
+        <v>581.83561132835</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D96" t="n">
         <v>2000</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>1304.29829245774</v>
+        <v>1304.93129816644</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D97" t="n">
         <v>2000</v>
       </c>
       <c r="E97" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>799.846368761998</v>
+        <v>801.622398110406</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
         <v>2000</v>
       </c>
       <c r="E98" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>413.984091876007</v>
+        <v>414.554226890283</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
         <v>2000</v>
       </c>
       <c r="E99" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>-333.882879682956</v>
+        <v>-343.012013597196</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D100" t="n">
         <v>2000</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" t="n">
-        <v>176.964199489195</v>
+        <v>177.177271014462</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" t="s">
         <v>14</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>16</v>
       </c>
       <c r="D101" t="n">
         <v>2001</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>409.337428112421</v>
+        <v>409.571378567029</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D102" t="n">
         <v>2001</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>687.800369111994</v>
+        <v>687.300535914065</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="n">
         <v>2001</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" t="n">
         <v>105.544778031136</v>
@@ -2524,179 +2510,179 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D104" t="n">
         <v>2001</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>568.699407007147</v>
+        <v>570.751548828905</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D105" t="n">
         <v>2001</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" t="n">
-        <v>1329.47795495596</v>
+        <v>1330.18737387591</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D106" t="n">
         <v>2001</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>813.7620257432</v>
+        <v>815.408078900483</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D107" t="n">
         <v>2001</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>401.573265102107</v>
+        <v>402.229466955441</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>2001</v>
       </c>
       <c r="E108" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>-389.438053166313</v>
+        <v>-396.265979183418</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D109" t="n">
         <v>2001</v>
       </c>
       <c r="E109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>174.706913925239</v>
+        <v>174.925306101834</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
         <v>14</v>
-      </c>
-      <c r="B110" t="s">
-        <v>15</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
       </c>
       <c r="D110" t="n">
         <v>2002</v>
       </c>
       <c r="E110" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>403.200633978597</v>
+        <v>403.487045822529</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D111" t="n">
         <v>2002</v>
       </c>
       <c r="E111" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>663.857002523772</v>
+        <v>663.353316144031</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D112" t="n">
         <v>2002</v>
       </c>
       <c r="E112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
         <v>105.047800018466</v>
@@ -2704,179 +2690,179 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D113" t="n">
         <v>2002</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>558.290728434365</v>
+        <v>560.485665110899</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D114" t="n">
         <v>2002</v>
       </c>
       <c r="E114" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F114" t="n">
-        <v>1351.9017688581</v>
+        <v>1352.67204789262</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" t="n">
         <v>2002</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
-        <v>822.486480520669</v>
+        <v>824.30987612179</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D116" t="n">
         <v>2002</v>
       </c>
       <c r="E116" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>402.143597496653</v>
+        <v>402.436657647014</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>2002</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>-382.263966827948</v>
+        <v>-384.727715648009</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D118" t="n">
         <v>2002</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>171.466114089921</v>
+        <v>171.689106512911</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" t="s">
         <v>14</v>
-      </c>
-      <c r="B119" t="s">
-        <v>15</v>
-      </c>
-      <c r="C119" t="s">
-        <v>16</v>
       </c>
       <c r="D119" t="n">
         <v>2003</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>394.00022572447</v>
+        <v>394.232799312029</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="n">
         <v>2003</v>
       </c>
       <c r="E120" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F120" t="n">
-        <v>676.585604749468</v>
+        <v>676.087789703944</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D121" t="n">
         <v>2003</v>
       </c>
       <c r="E121" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F121" t="n">
         <v>104.511411261828</v>
@@ -2884,179 +2870,179 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D122" t="n">
         <v>2003</v>
       </c>
       <c r="E122" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
-        <v>562.542109368099</v>
+        <v>564.76281278938</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D123" t="n">
         <v>2003</v>
       </c>
       <c r="E123" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F123" t="n">
-        <v>1403.55952676963</v>
+        <v>1404.32923767784</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" t="n">
         <v>2003</v>
       </c>
       <c r="E124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F124" t="n">
-        <v>831.655997468948</v>
+        <v>833.549230413974</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D125" t="n">
         <v>2003</v>
       </c>
       <c r="E125" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F125" t="n">
-        <v>412.711097108885</v>
+        <v>412.955426079208</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D126" t="n">
         <v>2003</v>
       </c>
       <c r="E126" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F126" t="n">
-        <v>-349.468352072702</v>
+        <v>-353.05525166066</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D127" t="n">
         <v>2003</v>
       </c>
       <c r="E127" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F127" t="n">
-        <v>168.881211409549</v>
+        <v>169.109236207693</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
         <v>14</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" t="s">
-        <v>16</v>
       </c>
       <c r="D128" t="n">
         <v>2004</v>
       </c>
       <c r="E128" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>394.099940776474</v>
+        <v>394.387312032763</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D129" t="n">
         <v>2004</v>
       </c>
       <c r="E129" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F129" t="n">
-        <v>671.528983856688</v>
+        <v>671.093968071841</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D130" t="n">
         <v>2004</v>
       </c>
       <c r="E130" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F130" t="n">
         <v>96.6708300841512</v>
@@ -3064,179 +3050,179 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C131" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D131" t="n">
         <v>2004</v>
       </c>
       <c r="E131" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>555.397702517877</v>
+        <v>557.511893988509</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C132" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D132" t="n">
         <v>2004</v>
       </c>
       <c r="E132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F132" t="n">
-        <v>1396.3881489982</v>
+        <v>1397.15555050172</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C133" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" t="n">
         <v>2004</v>
       </c>
       <c r="E133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F133" t="n">
-        <v>850.051583896162</v>
+        <v>851.993867635166</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D134" t="n">
         <v>2004</v>
       </c>
       <c r="E134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>429.280464502685</v>
+        <v>429.534156214893</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D135" t="n">
         <v>2004</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F135" t="n">
-        <v>-378.827714403003</v>
+        <v>-381.779605427638</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D136" t="n">
         <v>2004</v>
       </c>
       <c r="E136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F136" t="n">
-        <v>163.877462084825</v>
+        <v>164.111715898458</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137" t="s">
         <v>14</v>
-      </c>
-      <c r="B137" t="s">
-        <v>15</v>
-      </c>
-      <c r="C137" t="s">
-        <v>16</v>
       </c>
       <c r="D137" t="n">
         <v>2005</v>
       </c>
       <c r="E137" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>389.443924346164</v>
+        <v>389.680150383046</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D138" t="n">
         <v>2005</v>
       </c>
       <c r="E138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F138" t="n">
-        <v>673.191754111911</v>
+        <v>672.835731638426</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D139" t="n">
         <v>2005</v>
       </c>
       <c r="E139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F139" t="n">
         <v>95.3490273661817</v>
@@ -3244,179 +3230,179 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="n">
         <v>2005</v>
       </c>
       <c r="E140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F140" t="n">
-        <v>551.233699083821</v>
+        <v>553.447962717207</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D141" t="n">
         <v>2005</v>
       </c>
       <c r="E141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F141" t="n">
-        <v>1385.74926964312</v>
+        <v>1386.55570892828</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" t="n">
         <v>2005</v>
       </c>
       <c r="E142" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F142" t="n">
-        <v>849.535864106394</v>
+        <v>851.353640377485</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D143" t="n">
         <v>2005</v>
       </c>
       <c r="E143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>428.981732800529</v>
+        <v>429.270681565989</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D144" t="n">
         <v>2005</v>
       </c>
       <c r="E144" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>-377.844262200443</v>
+        <v>-382.708514178378</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D145" t="n">
         <v>2005</v>
       </c>
       <c r="E145" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>159.018738403678</v>
+        <v>159.257508289584</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" t="s">
         <v>14</v>
-      </c>
-      <c r="B146" t="s">
-        <v>15</v>
-      </c>
-      <c r="C146" t="s">
-        <v>16</v>
       </c>
       <c r="D146" t="n">
         <v>2006</v>
       </c>
       <c r="E146" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>386.45178775719</v>
+        <v>386.651697498182</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
         <v>2006</v>
       </c>
       <c r="E147" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F147" t="n">
-        <v>671.032600605299</v>
+        <v>670.673109201849</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D148" t="n">
         <v>2006</v>
       </c>
       <c r="E148" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F148" t="n">
         <v>92.6478632174243</v>
@@ -3424,179 +3410,179 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D149" t="n">
         <v>2006</v>
       </c>
       <c r="E149" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F149" t="n">
-        <v>540.771501162426</v>
+        <v>543.066074831482</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C150" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D150" t="n">
         <v>2006</v>
       </c>
       <c r="E150" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F150" t="n">
-        <v>1393.89416787286</v>
+        <v>1394.72192569298</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C151" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D151" t="n">
         <v>2006</v>
       </c>
       <c r="E151" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F151" t="n">
-        <v>862.782613088959</v>
+        <v>864.55613019401</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D152" t="n">
         <v>2006</v>
       </c>
       <c r="E152" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F152" t="n">
-        <v>432.405179429667</v>
+        <v>432.665102790319</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D153" t="n">
         <v>2006</v>
       </c>
       <c r="E153" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F153" t="n">
-        <v>-385.625103491304</v>
+        <v>-390.880171333523</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C154" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D154" t="n">
         <v>2006</v>
       </c>
       <c r="E154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>155.279358425752</v>
+        <v>155.522153671104</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
         <v>14</v>
-      </c>
-      <c r="B155" t="s">
-        <v>15</v>
-      </c>
-      <c r="C155" t="s">
-        <v>16</v>
       </c>
       <c r="D155" t="n">
         <v>2007</v>
       </c>
       <c r="E155" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F155" t="n">
-        <v>390.351840383911</v>
+        <v>390.673822145371</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D156" t="n">
         <v>2007</v>
       </c>
       <c r="E156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F156" t="n">
-        <v>595.606810961621</v>
+        <v>595.196092912042</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D157" t="n">
         <v>2007</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F157" t="n">
         <v>88.6902110502673</v>
@@ -3604,179 +3590,179 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D158" t="n">
         <v>2007</v>
       </c>
       <c r="E158" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F158" t="n">
-        <v>546.74887726211</v>
+        <v>549.024162646295</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D159" t="n">
         <v>2007</v>
       </c>
       <c r="E159" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F159" t="n">
-        <v>1401.71261420689</v>
+        <v>1402.55369563834</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D160" t="n">
         <v>2007</v>
       </c>
       <c r="E160" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>864.225513896249</v>
+        <v>865.991199575875</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D161" t="n">
         <v>2007</v>
       </c>
       <c r="E161" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F161" t="n">
-        <v>444.442383749122</v>
+        <v>444.868146726001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D162" t="n">
         <v>2007</v>
       </c>
       <c r="E162" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F162" t="n">
-        <v>-331.877169713367</v>
+        <v>-337.66301559224</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D163" t="n">
         <v>2007</v>
       </c>
       <c r="E163" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>150.928900689979</v>
+        <v>151.177135636189</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
         <v>14</v>
-      </c>
-      <c r="B164" t="s">
-        <v>15</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
       </c>
       <c r="D164" t="n">
         <v>2008</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>386.411607015687</v>
+        <v>386.672378972437</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D165" t="n">
         <v>2008</v>
       </c>
       <c r="E165" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F165" t="n">
-        <v>639.593904000389</v>
+        <v>639.139002991667</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D166" t="n">
         <v>2008</v>
       </c>
       <c r="E166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F166" t="n">
         <v>87.4731660529321</v>
@@ -3784,179 +3770,179 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D167" t="n">
         <v>2008</v>
       </c>
       <c r="E167" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>527.025984471018</v>
+        <v>529.30356335966</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D168" t="n">
         <v>2008</v>
       </c>
       <c r="E168" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F168" t="n">
-        <v>1334.7414569519</v>
+        <v>1335.53175619427</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D169" t="n">
         <v>2008</v>
       </c>
       <c r="E169" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F169" t="n">
-        <v>845.263906844565</v>
+        <v>847.017914996818</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C170" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D170" t="n">
         <v>2008</v>
       </c>
       <c r="E170" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>419.409857119109</v>
+        <v>419.760918513414</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D171" t="n">
         <v>2008</v>
       </c>
       <c r="E171" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F171" t="n">
-        <v>-380.743681381543</v>
+        <v>-386.3534333876</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D172" t="n">
         <v>2008</v>
       </c>
       <c r="E172" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F172" t="n">
-        <v>146.783103549684</v>
+        <v>147.037583527466</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" t="s">
         <v>14</v>
-      </c>
-      <c r="B173" t="s">
-        <v>15</v>
-      </c>
-      <c r="C173" t="s">
-        <v>16</v>
       </c>
       <c r="D173" t="n">
         <v>2009</v>
       </c>
       <c r="E173" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F173" t="n">
-        <v>382.367693033932</v>
+        <v>382.582341256757</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D174" t="n">
         <v>2009</v>
       </c>
       <c r="E174" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F174" t="n">
-        <v>626.197332376046</v>
+        <v>625.503712124033</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C175" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D175" t="n">
         <v>2009</v>
       </c>
       <c r="E175" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
         <v>80.5891570798192</v>
@@ -3964,179 +3950,179 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D176" t="n">
         <v>2009</v>
       </c>
       <c r="E176" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>439.513985314869</v>
+        <v>442.107561432475</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C177" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D177" t="n">
         <v>2009</v>
       </c>
       <c r="E177" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F177" t="n">
-        <v>1243.44423574807</v>
+        <v>1244.246923838</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D178" t="n">
         <v>2009</v>
       </c>
       <c r="E178" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F178" t="n">
-        <v>823.718848507668</v>
+        <v>825.406828726842</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D179" t="n">
         <v>2009</v>
       </c>
       <c r="E179" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F179" t="n">
-        <v>346.860597421438</v>
+        <v>347.178183378787</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D180" t="n">
         <v>2009</v>
       </c>
       <c r="E180" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F180" t="n">
-        <v>-377.099928788224</v>
+        <v>-383.059868915005</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D181" t="n">
         <v>2009</v>
       </c>
       <c r="E181" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F181" t="n">
-        <v>144.869791334607</v>
+        <v>145.140964694808</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182" t="s">
         <v>14</v>
-      </c>
-      <c r="B182" t="s">
-        <v>15</v>
-      </c>
-      <c r="C182" t="s">
-        <v>16</v>
       </c>
       <c r="D182" t="n">
         <v>2010</v>
       </c>
       <c r="E182" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F182" t="n">
-        <v>378.761022987298</v>
+        <v>378.968430250594</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D183" t="n">
         <v>2010</v>
       </c>
       <c r="E183" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F183" t="n">
-        <v>658.66660745233</v>
+        <v>658.020884785507</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D184" t="n">
         <v>2010</v>
       </c>
       <c r="E184" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F184" t="n">
         <v>80.1246779243071</v>
@@ -4144,179 +4130,179 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D185" t="n">
         <v>2010</v>
       </c>
       <c r="E185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F185" t="n">
-        <v>469.149476469018</v>
+        <v>472.195564534162</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D186" t="n">
         <v>2010</v>
       </c>
       <c r="E186" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F186" t="n">
-        <v>1255.76296047161</v>
+        <v>1256.44014878011</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D187" t="n">
         <v>2010</v>
       </c>
       <c r="E187" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>817.828743347843</v>
+        <v>819.562577513179</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C188" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D188" t="n">
         <v>2010</v>
       </c>
       <c r="E188" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F188" t="n">
-        <v>363.58863837793</v>
+        <v>364.158260911068</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C189" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D189" t="n">
         <v>2010</v>
       </c>
       <c r="E189" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F189" t="n">
-        <v>-372.352004833072</v>
+        <v>-378.671770849729</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D190" t="n">
         <v>2010</v>
       </c>
       <c r="E190" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F190" t="n">
-        <v>141.442620357129</v>
+        <v>141.746392564725</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
+        <v>12</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
         <v>14</v>
-      </c>
-      <c r="B191" t="s">
-        <v>15</v>
-      </c>
-      <c r="C191" t="s">
-        <v>16</v>
       </c>
       <c r="D191" t="n">
         <v>2011</v>
       </c>
       <c r="E191" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F191" t="n">
-        <v>375.489249818956</v>
+        <v>375.680969136915</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D192" t="n">
         <v>2011</v>
       </c>
       <c r="E192" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>584.864794230538</v>
+        <v>583.958110808892</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D193" t="n">
         <v>2011</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F193" t="n">
         <v>79.6016213320552</v>
@@ -4324,179 +4310,179 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D194" t="n">
         <v>2011</v>
       </c>
       <c r="E194" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F194" t="n">
-        <v>457.637948927825</v>
+        <v>460.485116660447</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D195" t="n">
         <v>2011</v>
       </c>
       <c r="E195" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F195" t="n">
-        <v>1242.65154281353</v>
+        <v>1243.34520490697</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C196" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D196" t="n">
         <v>2011</v>
       </c>
       <c r="E196" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>808.31001103822</v>
+        <v>810.051154772734</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C197" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D197" t="n">
         <v>2011</v>
       </c>
       <c r="E197" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F197" t="n">
-        <v>363.15169137907</v>
+        <v>363.939514530402</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C198" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D198" t="n">
         <v>2011</v>
       </c>
       <c r="E198" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>-357.766750932821</v>
+        <v>-363.100628818835</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D199" t="n">
         <v>2011</v>
       </c>
       <c r="E199" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F199" t="n">
-        <v>136.964840413603</v>
+        <v>137.293399656952</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
         <v>14</v>
-      </c>
-      <c r="B200" t="s">
-        <v>15</v>
-      </c>
-      <c r="C200" t="s">
-        <v>16</v>
       </c>
       <c r="D200" t="n">
         <v>2012</v>
       </c>
       <c r="E200" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F200" t="n">
-        <v>374.515340014826</v>
+        <v>374.752928289095</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D201" t="n">
         <v>2012</v>
       </c>
       <c r="E201" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F201" t="n">
-        <v>594.872579894015</v>
+        <v>594.008149153509</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D202" t="n">
         <v>2012</v>
       </c>
       <c r="E202" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>78.8163996572504</v>
@@ -4504,179 +4490,179 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D203" t="n">
         <v>2012</v>
       </c>
       <c r="E203" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F203" t="n">
-        <v>440.39044092231</v>
+        <v>443.211935648427</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C204" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D204" t="n">
         <v>2012</v>
       </c>
       <c r="E204" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F204" t="n">
-        <v>1227.70791757475</v>
+        <v>1228.39067392374</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D205" t="n">
         <v>2012</v>
       </c>
       <c r="E205" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F205" t="n">
-        <v>778.731483976142</v>
+        <v>780.485604968023</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D206" t="n">
         <v>2012</v>
       </c>
       <c r="E206" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F206" t="n">
-        <v>347.880643837136</v>
+        <v>348.717542199638</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C207" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D207" t="n">
         <v>2012</v>
       </c>
       <c r="E207" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F207" t="n">
-        <v>-369.17758603411</v>
+        <v>-375.457106147434</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C208" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D208" t="n">
         <v>2012</v>
       </c>
       <c r="E208" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>133.940265322628</v>
+        <v>134.290174646277</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
+        <v>12</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
         <v>14</v>
-      </c>
-      <c r="B209" t="s">
-        <v>15</v>
-      </c>
-      <c r="C209" t="s">
-        <v>16</v>
       </c>
       <c r="D209" t="n">
         <v>2013</v>
       </c>
       <c r="E209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F209" t="n">
-        <v>378.25236802756</v>
+        <v>378.475531834558</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D210" t="n">
         <v>2013</v>
       </c>
       <c r="E210" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F210" t="n">
-        <v>599.842205835672</v>
+        <v>598.887560614239</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D211" t="n">
         <v>2013</v>
       </c>
       <c r="E211" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F211" t="n">
         <v>77.9876800363124</v>
@@ -4684,179 +4670,179 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D212" t="n">
         <v>2013</v>
       </c>
       <c r="E212" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F212" t="n">
-        <v>424.640972080557</v>
+        <v>428.120218918589</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D213" t="n">
         <v>2013</v>
       </c>
       <c r="E213" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>1165.47329116085</v>
+        <v>1166.16329279262</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D214" t="n">
         <v>2013</v>
       </c>
       <c r="E214" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>772.612213951286</v>
+        <v>774.35602601002</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D215" t="n">
         <v>2013</v>
       </c>
       <c r="E215" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F215" t="n">
-        <v>344.73459527799</v>
+        <v>345.795573759698</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D216" t="n">
         <v>2013</v>
       </c>
       <c r="E216" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F216" t="n">
-        <v>-361.467882372576</v>
+        <v>-366.686103268182</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D217" t="n">
         <v>2013</v>
       </c>
       <c r="E217" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F217" t="n">
-        <v>128.430112014465</v>
+        <v>128.796508405893</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
+        <v>12</v>
+      </c>
+      <c r="B218" t="s">
+        <v>13</v>
+      </c>
+      <c r="C218" t="s">
         <v>14</v>
-      </c>
-      <c r="B218" t="s">
-        <v>15</v>
-      </c>
-      <c r="C218" t="s">
-        <v>16</v>
       </c>
       <c r="D218" t="n">
         <v>2014</v>
       </c>
       <c r="E218" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F218" t="n">
-        <v>382.535175489455</v>
+        <v>382.8118820875</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D219" t="n">
         <v>2014</v>
       </c>
       <c r="E219" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F219" t="n">
-        <v>522.631282987579</v>
+        <v>521.466423504357</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D220" t="n">
         <v>2014</v>
       </c>
       <c r="E220" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F220" t="n">
         <v>75.0324932944216</v>
@@ -4864,179 +4850,179 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D221" t="n">
         <v>2014</v>
       </c>
       <c r="E221" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F221" t="n">
-        <v>408.098207323202</v>
+        <v>412.6366464112</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C222" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D222" t="n">
         <v>2014</v>
       </c>
       <c r="E222" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F222" t="n">
-        <v>1104.1442089571</v>
+        <v>1104.86952624322</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D223" t="n">
         <v>2014</v>
       </c>
       <c r="E223" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F223" t="n">
-        <v>778.512791452496</v>
+        <v>780.205422330091</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C224" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D224" t="n">
         <v>2014</v>
       </c>
       <c r="E224" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>351.478666911578</v>
+        <v>352.750392368864</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D225" t="n">
         <v>2014</v>
       </c>
       <c r="E225" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F225" t="n">
-        <v>-338.199697082049</v>
+        <v>-342.791715313489</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D226" t="n">
         <v>2014</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F226" t="n">
-        <v>124.433084178075</v>
+        <v>124.817287743962</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" t="s">
+        <v>13</v>
+      </c>
+      <c r="C227" t="s">
         <v>14</v>
-      </c>
-      <c r="B227" t="s">
-        <v>15</v>
-      </c>
-      <c r="C227" t="s">
-        <v>16</v>
       </c>
       <c r="D227" t="n">
         <v>2015</v>
       </c>
       <c r="E227" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F227" t="n">
-        <v>381.686414263094</v>
+        <v>382.137407216639</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D228" t="n">
         <v>2015</v>
       </c>
       <c r="E228" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F228" t="n">
-        <v>546.105369075579</v>
+        <v>545.128924724654</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D229" t="n">
         <v>2015</v>
       </c>
       <c r="E229" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F229" t="n">
         <v>74.430542746511</v>
@@ -5044,179 +5030,179 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D230" t="n">
         <v>2015</v>
       </c>
       <c r="E230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>418.095344722348</v>
+        <v>422.35926216855</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D231" t="n">
         <v>2015</v>
       </c>
       <c r="E231" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F231" t="n">
-        <v>1112.45107840313</v>
+        <v>1113.16320387052</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C232" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D232" t="n">
         <v>2015</v>
       </c>
       <c r="E232" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F232" t="n">
-        <v>794.052449264832</v>
+        <v>795.756195977981</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D233" t="n">
         <v>2015</v>
       </c>
       <c r="E233" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>341.547846263349</v>
+        <v>342.887843966889</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C234" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D234" t="n">
         <v>2015</v>
       </c>
       <c r="E234" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>-331.261737412199</v>
+        <v>-336.186559766275</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D235" t="n">
         <v>2015</v>
       </c>
       <c r="E235" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>122.444842852262</v>
+        <v>122.843468038302</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" t="s">
         <v>14</v>
-      </c>
-      <c r="B236" t="s">
-        <v>15</v>
-      </c>
-      <c r="C236" t="s">
-        <v>16</v>
       </c>
       <c r="D236" t="n">
         <v>2016</v>
       </c>
       <c r="E236" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F236" t="n">
-        <v>385.474385659826</v>
+        <v>385.79898732434</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C237" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D237" t="n">
         <v>2016</v>
       </c>
       <c r="E237" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F237" t="n">
-        <v>551.48171362834</v>
+        <v>550.702435069222</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C238" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D238" t="n">
         <v>2016</v>
       </c>
       <c r="E238" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F238" t="n">
         <v>71.529545545712</v>
@@ -5224,179 +5210,179 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D239" t="n">
         <v>2016</v>
       </c>
       <c r="E239" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F239" t="n">
-        <v>421.192557782467</v>
+        <v>426.05530577665</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C240" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D240" t="n">
         <v>2016</v>
       </c>
       <c r="E240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F240" t="n">
-        <v>1088.14983836878</v>
+        <v>1088.90202800122</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C241" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D241" t="n">
         <v>2016</v>
       </c>
       <c r="E241" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F241" t="n">
-        <v>811.59181029332</v>
+        <v>813.383343727409</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D242" t="n">
         <v>2016</v>
       </c>
       <c r="E242" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F242" t="n">
-        <v>343.866683446683</v>
+        <v>345.548171577652</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C243" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D243" t="n">
         <v>2016</v>
       </c>
       <c r="E243" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F243" t="n">
-        <v>-324.527969644795</v>
+        <v>-327.145621444847</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C244" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D244" t="n">
         <v>2016</v>
       </c>
       <c r="E244" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F244" t="n">
-        <v>119.83460852882</v>
+        <v>120.254687584334</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
+        <v>12</v>
+      </c>
+      <c r="B245" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" t="s">
         <v>14</v>
-      </c>
-      <c r="B245" t="s">
-        <v>15</v>
-      </c>
-      <c r="C245" t="s">
-        <v>16</v>
       </c>
       <c r="D245" t="n">
         <v>2017</v>
       </c>
       <c r="E245" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F245" t="n">
-        <v>386.99441476966</v>
+        <v>386.999239380273</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D246" t="n">
         <v>2017</v>
       </c>
       <c r="E246" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F246" t="n">
-        <v>550.379270203053</v>
+        <v>549.279520518761</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C247" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D247" t="n">
         <v>2017</v>
       </c>
       <c r="E247" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F247" t="n">
         <v>70.8580004126779</v>
@@ -5404,179 +5390,179 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D248" t="n">
         <v>2017</v>
       </c>
       <c r="E248" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F248" t="n">
-        <v>429.111760865942</v>
+        <v>434.327341917065</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D249" t="n">
         <v>2017</v>
       </c>
       <c r="E249" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F249" t="n">
-        <v>1085.06405718584</v>
+        <v>1085.75575040189</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C250" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D250" t="n">
         <v>2017</v>
       </c>
       <c r="E250" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F250" t="n">
-        <v>826.323397755239</v>
+        <v>828.146572989862</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D251" t="n">
         <v>2017</v>
       </c>
       <c r="E251" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F251" t="n">
-        <v>350.106083825623</v>
+        <v>351.997578863217</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C252" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D252" t="n">
         <v>2017</v>
       </c>
       <c r="E252" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>-268.241896748777</v>
+        <v>-271.843126590274</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C253" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D253" t="n">
         <v>2017</v>
       </c>
       <c r="E253" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F253" t="n">
-        <v>118.798582229695</v>
+        <v>119.231333072515</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" t="s">
         <v>14</v>
-      </c>
-      <c r="B254" t="s">
-        <v>15</v>
-      </c>
-      <c r="C254" t="s">
-        <v>16</v>
       </c>
       <c r="D254" t="n">
         <v>2018</v>
       </c>
       <c r="E254" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>381.231022144669</v>
+        <v>381.157510578263</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C255" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D255" t="n">
         <v>2018</v>
       </c>
       <c r="E255" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F255" t="n">
-        <v>539.475767849646</v>
+        <v>537.781743613974</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C256" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D256" t="n">
         <v>2018</v>
       </c>
       <c r="E256" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F256" t="n">
         <v>67.3089219723679</v>
@@ -5584,1202 +5570,1202 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D257" t="n">
         <v>2018</v>
       </c>
       <c r="E257" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>428.777634713372</v>
+        <v>434.570638284796</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C258" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D258" t="n">
         <v>2018</v>
       </c>
       <c r="E258" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F258" t="n">
-        <v>1023.39818058897</v>
+        <v>1024.12362106162</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C259" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D259" t="n">
         <v>2018</v>
       </c>
       <c r="E259" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F259" t="n">
-        <v>829.000831343403</v>
+        <v>830.903660101338</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C260" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D260" t="n">
         <v>2018</v>
       </c>
       <c r="E260" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F260" t="n">
-        <v>342.946186684051</v>
+        <v>344.983302531057</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C261" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D261" t="n">
         <v>2018</v>
       </c>
       <c r="E261" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>-229.684213304138</v>
+        <v>-239.324393665273</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C262" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D262" t="n">
         <v>2018</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>117.51985075594</v>
+        <v>117.967148064907</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263" t="s">
+        <v>13</v>
+      </c>
+      <c r="C263" t="s">
         <v>14</v>
-      </c>
-      <c r="B263" t="s">
-        <v>15</v>
-      </c>
-      <c r="C263" t="s">
-        <v>16</v>
       </c>
       <c r="D263" t="n">
         <v>2019</v>
       </c>
       <c r="E263" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>378.017603999888</v>
+        <v>378.614518121346</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C264" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D264" t="n">
         <v>2019</v>
       </c>
       <c r="E264" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F264" t="n">
-        <v>529.402428348165</v>
+        <v>527.582540800113</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C265" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D265" t="n">
         <v>2019</v>
       </c>
       <c r="E265" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F265" t="n">
-        <v>60.7370354029492</v>
+        <v>60.7371413329492</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C266" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D266" t="n">
         <v>2019</v>
       </c>
       <c r="E266" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F266" t="n">
-        <v>417.60914612192</v>
+        <v>423.739082988637</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D267" t="n">
         <v>2019</v>
       </c>
       <c r="E267" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F267" t="n">
-        <v>903.835773179493</v>
+        <v>904.506790966212</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D268" t="n">
         <v>2019</v>
       </c>
       <c r="E268" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F268" t="n">
-        <v>834.431192487351</v>
+        <v>836.287786323883</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D269" t="n">
         <v>2019</v>
       </c>
       <c r="E269" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F269" t="n">
-        <v>329.832051558101</v>
+        <v>331.778328277048</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C270" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D270" t="n">
         <v>2019</v>
       </c>
       <c r="E270" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F270" t="n">
-        <v>-227.098507438159</v>
+        <v>-233.803038618847</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D271" t="n">
         <v>2019</v>
       </c>
       <c r="E271" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" t="n">
-        <v>116.674885007893</v>
+        <v>117.097886308101</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B272" t="s">
+        <v>13</v>
+      </c>
+      <c r="C272" t="s">
         <v>14</v>
-      </c>
-      <c r="B272" t="s">
-        <v>15</v>
-      </c>
-      <c r="C272" t="s">
-        <v>16</v>
       </c>
       <c r="D272" t="n">
         <v>2020</v>
       </c>
       <c r="E272" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>380.002894363114</v>
+        <v>380.936076868425</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D273" t="n">
         <v>2020</v>
       </c>
       <c r="E273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F273" t="n">
-        <v>522.790182228603</v>
+        <v>521.275031731589</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C274" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D274" t="n">
         <v>2020</v>
       </c>
       <c r="E274" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F274" t="n">
-        <v>55.788005659586</v>
+        <v>55.788271057392</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D275" t="n">
         <v>2020</v>
       </c>
       <c r="E275" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F275" t="n">
-        <v>397.753770267989</v>
+        <v>403.198020838051</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D276" t="n">
         <v>2020</v>
       </c>
       <c r="E276" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F276" t="n">
-        <v>776.858409946389</v>
+        <v>777.45504542698</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D277" t="n">
         <v>2020</v>
       </c>
       <c r="E277" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F277" t="n">
-        <v>722.260190505395</v>
+        <v>723.881520661935</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D278" t="n">
         <v>2020</v>
       </c>
       <c r="E278" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F278" t="n">
-        <v>305.131430704928</v>
+        <v>307.000463074576</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D279" t="n">
         <v>2020</v>
       </c>
       <c r="E279" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F279" t="n">
-        <v>-227.035750142288</v>
+        <v>-237.439962869101</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D280" t="n">
         <v>2020</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F280" t="n">
-        <v>116.142206801177</v>
+        <v>116.565658631295</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" t="s">
+        <v>13</v>
+      </c>
+      <c r="C281" t="s">
         <v>14</v>
-      </c>
-      <c r="B281" t="s">
-        <v>15</v>
-      </c>
-      <c r="C281" t="s">
-        <v>16</v>
       </c>
       <c r="D281" t="n">
         <v>2021</v>
       </c>
       <c r="E281" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F281" t="n">
-        <v>377.360547166025</v>
+        <v>378.456442658931</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D282" t="n">
         <v>2021</v>
       </c>
       <c r="E282" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F282" t="n">
-        <v>535.425443934679</v>
+        <v>534.198914957924</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D283" t="n">
         <v>2021</v>
       </c>
       <c r="E283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F283" t="n">
-        <v>54.0029681034406</v>
+        <v>54.0035470442178</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D284" t="n">
         <v>2021</v>
       </c>
       <c r="E284" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F284" t="n">
-        <v>427.551636610786</v>
+        <v>432.610561777493</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D285" t="n">
         <v>2021</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F285" t="n">
-        <v>839.728254468277</v>
+        <v>840.378564117871</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D286" t="n">
         <v>2021</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F286" t="n">
-        <v>783.424776044919</v>
+        <v>785.177055609558</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D287" t="n">
         <v>2021</v>
       </c>
       <c r="E287" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F287" t="n">
-        <v>315.478610097926</v>
+        <v>317.36450825643</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D288" t="n">
         <v>2021</v>
       </c>
       <c r="E288" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>-221.022743936707</v>
+        <v>-225.631263537836</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D289" t="n">
         <v>2021</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F289" t="n">
-        <v>114.967022218503</v>
+        <v>115.378268416337</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>13</v>
+      </c>
+      <c r="C290" t="s">
         <v>14</v>
-      </c>
-      <c r="B290" t="s">
-        <v>15</v>
-      </c>
-      <c r="C290" t="s">
-        <v>16</v>
       </c>
       <c r="D290" t="n">
         <v>2022</v>
       </c>
       <c r="E290" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F290" t="n">
-        <v>363.176714632132</v>
+        <v>364.65677975327</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D291" t="n">
         <v>2022</v>
       </c>
       <c r="E291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F291" t="n">
-        <v>478.507920188267</v>
+        <v>476.648726158465</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D292" t="n">
         <v>2022</v>
       </c>
       <c r="E292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F292" t="n">
-        <v>52.0935425958534</v>
+        <v>52.0940424366287</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D293" t="n">
         <v>2022</v>
       </c>
       <c r="E293" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F293" t="n">
-        <v>389.702943127021</v>
+        <v>394.458487720157</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D294" t="n">
         <v>2022</v>
       </c>
       <c r="E294" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F294" t="n">
-        <v>864.667655569419</v>
+        <v>865.866043714366</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D295" t="n">
         <v>2022</v>
       </c>
       <c r="E295" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F295" t="n">
-        <v>804.501606792756</v>
+        <v>806.245050946072</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D296" t="n">
         <v>2022</v>
       </c>
       <c r="E296" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F296" t="n">
-        <v>288.875145879195</v>
+        <v>290.866075172269</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D297" t="n">
         <v>2022</v>
       </c>
       <c r="E297" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F297" t="n">
-        <v>-215.946021425041</v>
+        <v>-220.559672255561</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D298" t="n">
         <v>2022</v>
       </c>
       <c r="E298" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F298" t="n">
-        <v>113.79969900673</v>
+        <v>114.280342861803</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
         <v>14</v>
-      </c>
-      <c r="B299" t="s">
-        <v>15</v>
-      </c>
-      <c r="C299" t="s">
-        <v>16</v>
       </c>
       <c r="D299" t="n">
         <v>2023</v>
       </c>
       <c r="E299" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F299" t="n">
-        <v>362.373590367912</v>
+        <v>363.619563591554</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D300" t="n">
         <v>2023</v>
       </c>
       <c r="E300" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F300" t="n">
-        <v>445.961277654948</v>
+        <v>445.613900685171</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D301" t="n">
         <v>2023</v>
       </c>
       <c r="E301" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F301" t="n">
-        <v>47.8909230208003</v>
+        <v>47.89283934417</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D302" t="n">
         <v>2023</v>
       </c>
       <c r="E302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F302" t="n">
-        <v>358.325413427002</v>
+        <v>362.417138597088</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D303" t="n">
         <v>2023</v>
       </c>
       <c r="E303" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F303" t="n">
-        <v>699.007440525757</v>
+        <v>699.37918405304</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D304" t="n">
         <v>2023</v>
       </c>
       <c r="E304" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>795.551994752812</v>
+        <v>797.146235086097</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D305" t="n">
         <v>2023</v>
       </c>
       <c r="E305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F305" t="n">
-        <v>262.985463486059</v>
+        <v>264.715418515633</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D306" t="n">
         <v>2023</v>
       </c>
       <c r="E306" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F306" t="n">
-        <v>-214.221182241498</v>
+        <v>-215.366950497865</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C307" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D307" t="n">
         <v>2023</v>
       </c>
       <c r="E307" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F307" t="n">
-        <v>112.762646830595</v>
+        <v>113.204799545644</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" t="s">
         <v>14</v>
-      </c>
-      <c r="B308" t="s">
-        <v>15</v>
-      </c>
-      <c r="C308" t="s">
-        <v>16</v>
       </c>
       <c r="D308" t="n">
         <v>2024</v>
       </c>
       <c r="E308" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F308" t="n">
-        <v>284.835456323495</v>
+        <v>353.177513845974</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B309" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C309" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D309" t="n">
         <v>2024</v>
       </c>
       <c r="E309" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F309" t="n">
-        <v>366.668325238157</v>
+        <v>428.822980211391</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B310" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C310" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D310" t="n">
         <v>2024</v>
       </c>
       <c r="E310" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F310" t="n">
-        <v>43.0841214436329</v>
+        <v>45.3381911005699</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C311" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D311" t="n">
         <v>2024</v>
       </c>
       <c r="E311" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F311" t="n">
-        <v>310.661825346861</v>
+        <v>349.219056656656</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B312" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C312" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D312" t="n">
         <v>2024</v>
       </c>
       <c r="E312" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F312" t="n">
-        <v>601.301537339903</v>
+        <v>634.595728653527</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B313" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C313" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D313" t="n">
         <v>2024</v>
       </c>
       <c r="E313" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F313" t="n">
-        <v>661.869941658049</v>
+        <v>792.215181953101</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B314" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C314" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D314" t="n">
         <v>2024</v>
       </c>
       <c r="E314" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F314" t="n">
-        <v>219.925989978777</v>
+        <v>255.296238997502</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B315" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C315" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D315" t="n">
         <v>2024</v>
       </c>
       <c r="E315" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F315" t="n">
-        <v>-182.624425711015</v>
+        <v>-223.952189656652</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B316" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C316" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D316" t="n">
         <v>2024</v>
       </c>
       <c r="E316" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F316" t="n">
-        <v>88.513923356142</v>
+        <v>107.802659258882</v>
       </c>
     </row>
   </sheetData>

--- a/plots/countries/sectors/European Union-sectors.xlsx
+++ b/plots/countries/sectors/European Union-sectors.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Data sources</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
+    <t xml:space="preserve">Lamb, W. F. (2026). Tidy GHG Inventories (v2.1) [Data set]. Zenodo. https://doi.org/10.5281/zenodo.14512139</t>
   </si>
   <si>
     <t xml:space="preserve">country</t>
@@ -485,7 +485,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>487.78337171747</v>
+        <v>487.783432972437</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>164.953406195342</v>
+        <v>164.953136965342</v>
       </c>
     </row>
     <row r="5">
@@ -605,7 +605,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>450.146045519006</v>
+        <v>450.14588202247</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>-258.202356037772</v>
+        <v>-258.166524370222</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>185.570648266128</v>
+        <v>185.586428332462</v>
       </c>
     </row>
     <row r="11">
@@ -665,7 +665,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>459.899890663091</v>
+        <v>459.899952051063</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>151.688793335715</v>
+        <v>151.688513159715</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +725,7 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>679.125184533095</v>
+        <v>679.125237934449</v>
       </c>
     </row>
     <row r="15">
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>418.52760313307</v>
+        <v>418.527454001094</v>
       </c>
     </row>
     <row r="18">
@@ -805,7 +805,7 @@
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>-356.241752382451</v>
+        <v>-356.19030825263</v>
       </c>
     </row>
     <row r="19">
@@ -825,7 +825,7 @@
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>188.859007012889</v>
+        <v>188.8746023918</v>
       </c>
     </row>
     <row r="20">
@@ -845,7 +845,7 @@
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>439.352996445015</v>
+        <v>439.353054832046</v>
       </c>
     </row>
     <row r="21">
@@ -885,7 +885,7 @@
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>147.610132393333</v>
+        <v>147.609861044333</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>640.213095470336</v>
+        <v>640.213355479519</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>405.502899354604</v>
+        <v>405.493634612258</v>
       </c>
     </row>
     <row r="27">
@@ -985,7 +985,7 @@
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>-325.451849148455</v>
+        <v>-325.40591157507</v>
       </c>
     </row>
     <row r="28">
@@ -1005,7 +1005,7 @@
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>190.583353002783</v>
+        <v>190.599051114607</v>
       </c>
     </row>
     <row r="29">
@@ -1025,7 +1025,7 @@
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>427.459300208373</v>
+        <v>427.459367122259</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>146.920432040919</v>
+        <v>146.920174731919</v>
       </c>
     </row>
     <row r="32">
@@ -1085,7 +1085,7 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>620.237088925102</v>
+        <v>620.237357374851</v>
       </c>
     </row>
     <row r="33">
@@ -1145,7 +1145,7 @@
         <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>395.526095468799</v>
+        <v>395.516367684929</v>
       </c>
     </row>
     <row r="36">
@@ -1165,7 +1165,7 @@
         <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>-347.007602774162</v>
+        <v>-346.937679054802</v>
       </c>
     </row>
     <row r="37">
@@ -1185,7 +1185,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>190.55889717658</v>
+        <v>190.574460476995</v>
       </c>
     </row>
     <row r="38">
@@ -1205,7 +1205,7 @@
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>422.230207313558</v>
+        <v>422.230264178877</v>
       </c>
     </row>
     <row r="39">
@@ -1245,7 +1245,7 @@
         <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>142.70355064642</v>
+        <v>142.70329887542</v>
       </c>
     </row>
     <row r="41">
@@ -1265,7 +1265,7 @@
         <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>617.993996088603</v>
+        <v>617.994234005959</v>
       </c>
     </row>
     <row r="42">
@@ -1325,7 +1325,7 @@
         <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>419.032655681113</v>
+        <v>419.022378675091</v>
       </c>
     </row>
     <row r="45">
@@ -1345,7 +1345,7 @@
         <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>-344.831112288824</v>
+        <v>-344.782374292094</v>
       </c>
     </row>
     <row r="46">
@@ -1365,7 +1365,7 @@
         <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>189.527341881755</v>
+        <v>189.5429811355</v>
       </c>
     </row>
     <row r="47">
@@ -1385,7 +1385,7 @@
         <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>422.351880777335</v>
+        <v>422.351933262885</v>
       </c>
     </row>
     <row r="48">
@@ -1425,7 +1425,7 @@
         <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>141.348989792379</v>
+        <v>141.348777503379</v>
       </c>
     </row>
     <row r="50">
@@ -1445,7 +1445,7 @@
         <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>639.244149234641</v>
+        <v>639.244557480405</v>
       </c>
     </row>
     <row r="51">
@@ -1505,7 +1505,7 @@
         <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>430.667186273616</v>
+        <v>430.656308959579</v>
       </c>
     </row>
     <row r="54">
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>-372.284351544039</v>
+        <v>-372.232332530299</v>
       </c>
     </row>
     <row r="55">
@@ -1545,7 +1545,7 @@
         <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>189.070547547451</v>
+        <v>189.086214531714</v>
       </c>
     </row>
     <row r="56">
@@ -1565,7 +1565,7 @@
         <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>423.069604464441</v>
+        <v>423.06959615836</v>
       </c>
     </row>
     <row r="57">
@@ -1605,7 +1605,7 @@
         <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>137.350371427759</v>
+        <v>137.350192259759</v>
       </c>
     </row>
     <row r="59">
@@ -1625,7 +1625,7 @@
         <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>631.081846030062</v>
+        <v>631.082264338564</v>
       </c>
     </row>
     <row r="60">
@@ -1685,7 +1685,7 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>430.002551147515</v>
+        <v>429.990892509675</v>
       </c>
     </row>
     <row r="63">
@@ -1705,7 +1705,7 @@
         <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>-388.611394097803</v>
+        <v>-388.56467768585</v>
       </c>
     </row>
     <row r="64">
@@ -1725,7 +1725,7 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>187.497796921901</v>
+        <v>187.513503764799</v>
       </c>
     </row>
     <row r="65">
@@ -1745,7 +1745,7 @@
         <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>420.525247140324</v>
+        <v>420.525159534237</v>
       </c>
     </row>
     <row r="66">
@@ -1785,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="F67" t="n">
-        <v>135.788567458484</v>
+        <v>135.788391469484</v>
       </c>
     </row>
     <row r="68">
@@ -1805,7 +1805,7 @@
         <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>622.531762925531</v>
+        <v>622.524407835531</v>
       </c>
     </row>
     <row r="69">
@@ -1865,7 +1865,7 @@
         <v>15</v>
       </c>
       <c r="F71" t="n">
-        <v>434.895152739708</v>
+        <v>434.894867908476</v>
       </c>
     </row>
     <row r="72">
@@ -1885,7 +1885,7 @@
         <v>15</v>
       </c>
       <c r="F72" t="n">
-        <v>-377.412440750172</v>
+        <v>-377.359473406794</v>
       </c>
     </row>
     <row r="73">
@@ -1905,7 +1905,7 @@
         <v>15</v>
       </c>
       <c r="F73" t="n">
-        <v>184.619635542285</v>
+        <v>184.635406591102</v>
       </c>
     </row>
     <row r="74">
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>417.87323981503</v>
+        <v>417.873056505274</v>
       </c>
     </row>
     <row r="75">
@@ -1965,7 +1965,7 @@
         <v>15</v>
       </c>
       <c r="F76" t="n">
-        <v>127.936789967835</v>
+        <v>127.936621975835</v>
       </c>
     </row>
     <row r="77">
@@ -1985,7 +1985,7 @@
         <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>597.813192138818</v>
+        <v>597.805933826318</v>
       </c>
     </row>
     <row r="78">
@@ -2045,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>417.914536331463</v>
+        <v>417.914233329127</v>
       </c>
     </row>
     <row r="81">
@@ -2065,7 +2065,7 @@
         <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>-376.854973742779</v>
+        <v>-376.78129893846</v>
       </c>
     </row>
     <row r="82">
@@ -2085,7 +2085,7 @@
         <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>181.343121493076</v>
+        <v>181.358883853879</v>
       </c>
     </row>
     <row r="83">
@@ -2105,7 +2105,7 @@
         <v>15</v>
       </c>
       <c r="F83" t="n">
-        <v>414.663641575925</v>
+        <v>414.663314578763</v>
       </c>
     </row>
     <row r="84">
@@ -2145,7 +2145,7 @@
         <v>15</v>
       </c>
       <c r="F85" t="n">
-        <v>126.167009136869</v>
+        <v>126.166871394869</v>
       </c>
     </row>
     <row r="86">
@@ -2165,7 +2165,7 @@
         <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>583.391586721364</v>
+        <v>583.383070301364</v>
       </c>
     </row>
     <row r="87">
@@ -2225,7 +2225,7 @@
         <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>399.034907386146</v>
+        <v>399.034613295819</v>
       </c>
     </row>
     <row r="90">
@@ -2245,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>-383.796913832862</v>
+        <v>-383.714593252348</v>
       </c>
     </row>
     <row r="91">
@@ -2265,7 +2265,7 @@
         <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>178.388931890196</v>
+        <v>178.404600054146</v>
       </c>
     </row>
     <row r="92">
@@ -2285,7 +2285,7 @@
         <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>411.184144851338</v>
+        <v>411.183670689346</v>
       </c>
     </row>
     <row r="93">
@@ -2325,7 +2325,7 @@
         <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>110.648319148704</v>
+        <v>110.648070878704</v>
       </c>
     </row>
     <row r="95">
@@ -2345,7 +2345,7 @@
         <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>581.83561132835</v>
+        <v>581.826998130849</v>
       </c>
     </row>
     <row r="96">
@@ -2405,7 +2405,7 @@
         <v>15</v>
       </c>
       <c r="F98" t="n">
-        <v>414.554226890283</v>
+        <v>414.553910964995</v>
       </c>
     </row>
     <row r="99">
@@ -2425,7 +2425,7 @@
         <v>15</v>
       </c>
       <c r="F99" t="n">
-        <v>-343.012013597196</v>
+        <v>-342.931283181413</v>
       </c>
     </row>
     <row r="100">
@@ -2445,7 +2445,7 @@
         <v>15</v>
       </c>
       <c r="F100" t="n">
-        <v>177.177271014462</v>
+        <v>177.191708135383</v>
       </c>
     </row>
     <row r="101">
@@ -2465,7 +2465,7 @@
         <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>409.571378567029</v>
+        <v>409.57104219886</v>
       </c>
     </row>
     <row r="102">
@@ -2505,7 +2505,7 @@
         <v>15</v>
       </c>
       <c r="F103" t="n">
-        <v>105.544778031136</v>
+        <v>105.544635031136</v>
       </c>
     </row>
     <row r="104">
@@ -2525,7 +2525,7 @@
         <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>570.751548828905</v>
+        <v>570.743322741405</v>
       </c>
     </row>
     <row r="105">
@@ -2565,7 +2565,7 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>815.408078900483</v>
+        <v>815.408084375528</v>
       </c>
     </row>
     <row r="107">
@@ -2585,7 +2585,7 @@
         <v>15</v>
       </c>
       <c r="F107" t="n">
-        <v>402.229466955441</v>
+        <v>402.229144449369</v>
       </c>
     </row>
     <row r="108">
@@ -2605,7 +2605,7 @@
         <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>-396.265979183418</v>
+        <v>-396.184819242449</v>
       </c>
     </row>
     <row r="109">
@@ -2625,7 +2625,7 @@
         <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>174.925306101834</v>
+        <v>174.939009326731</v>
       </c>
     </row>
     <row r="110">
@@ -2645,7 +2645,7 @@
         <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>403.487045822529</v>
+        <v>403.486859603375</v>
       </c>
     </row>
     <row r="111">
@@ -2685,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>105.047800018466</v>
+        <v>105.047657018466</v>
       </c>
     </row>
     <row r="113">
@@ -2705,7 +2705,7 @@
         <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>560.485665110899</v>
+        <v>560.478987463399</v>
       </c>
     </row>
     <row r="114">
@@ -2765,7 +2765,7 @@
         <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>402.436657647014</v>
+        <v>402.436352787326</v>
       </c>
     </row>
     <row r="117">
@@ -2785,7 +2785,7 @@
         <v>15</v>
       </c>
       <c r="F117" t="n">
-        <v>-384.727715648009</v>
+        <v>-384.651764261798</v>
       </c>
     </row>
     <row r="118">
@@ -2805,7 +2805,7 @@
         <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>171.689106512911</v>
+        <v>171.702811193536</v>
       </c>
     </row>
     <row r="119">
@@ -2825,7 +2825,7 @@
         <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>394.232799312029</v>
+        <v>394.232773739883</v>
       </c>
     </row>
     <row r="120">
@@ -2865,7 +2865,7 @@
         <v>15</v>
       </c>
       <c r="F121" t="n">
-        <v>104.511411261828</v>
+        <v>104.511290261828</v>
       </c>
     </row>
     <row r="122">
@@ -2885,7 +2885,7 @@
         <v>15</v>
       </c>
       <c r="F122" t="n">
-        <v>564.76281278938</v>
+        <v>564.75623191938</v>
       </c>
     </row>
     <row r="123">
@@ -2925,7 +2925,7 @@
         <v>15</v>
       </c>
       <c r="F124" t="n">
-        <v>833.549230413974</v>
+        <v>833.549235573936</v>
       </c>
     </row>
     <row r="125">
@@ -2945,7 +2945,7 @@
         <v>15</v>
       </c>
       <c r="F125" t="n">
-        <v>412.955426079208</v>
+        <v>412.955122045128</v>
       </c>
     </row>
     <row r="126">
@@ -2965,7 +2965,7 @@
         <v>15</v>
       </c>
       <c r="F126" t="n">
-        <v>-353.05525166066</v>
+        <v>-352.986495727719</v>
       </c>
     </row>
     <row r="127">
@@ -2985,7 +2985,7 @@
         <v>15</v>
       </c>
       <c r="F127" t="n">
-        <v>169.109236207693</v>
+        <v>169.122978914825</v>
       </c>
     </row>
     <row r="128">
@@ -3005,7 +3005,7 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>394.387312032763</v>
+        <v>394.387462216375</v>
       </c>
     </row>
     <row r="129">
@@ -3045,7 +3045,7 @@
         <v>15</v>
       </c>
       <c r="F130" t="n">
-        <v>96.6708300841512</v>
+        <v>96.6707640841512</v>
       </c>
     </row>
     <row r="131">
@@ -3065,7 +3065,7 @@
         <v>15</v>
       </c>
       <c r="F131" t="n">
-        <v>557.511893988509</v>
+        <v>557.505700228509</v>
       </c>
     </row>
     <row r="132">
@@ -3125,7 +3125,7 @@
         <v>15</v>
       </c>
       <c r="F134" t="n">
-        <v>429.534156214893</v>
+        <v>429.53387135952</v>
       </c>
     </row>
     <row r="135">
@@ -3145,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="F135" t="n">
-        <v>-381.779605427638</v>
+        <v>-381.714208826777</v>
       </c>
     </row>
     <row r="136">
@@ -3165,7 +3165,7 @@
         <v>15</v>
       </c>
       <c r="F136" t="n">
-        <v>164.111715898458</v>
+        <v>164.124763660869</v>
       </c>
     </row>
     <row r="137">
@@ -3185,7 +3185,7 @@
         <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>389.680150383046</v>
+        <v>389.680329854956</v>
       </c>
     </row>
     <row r="138">
@@ -3225,7 +3225,7 @@
         <v>15</v>
       </c>
       <c r="F139" t="n">
-        <v>95.3490273661817</v>
+        <v>95.3489613661817</v>
       </c>
     </row>
     <row r="140">
@@ -3285,7 +3285,7 @@
         <v>15</v>
       </c>
       <c r="F142" t="n">
-        <v>851.353640377485</v>
+        <v>851.353644707516</v>
       </c>
     </row>
     <row r="143">
@@ -3305,7 +3305,7 @@
         <v>15</v>
       </c>
       <c r="F143" t="n">
-        <v>429.270681565989</v>
+        <v>429.270415679557</v>
       </c>
     </row>
     <row r="144">
@@ -3325,7 +3325,7 @@
         <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>-382.708514178378</v>
+        <v>-382.63401608537</v>
       </c>
     </row>
     <row r="145">
@@ -3345,7 +3345,7 @@
         <v>15</v>
       </c>
       <c r="F145" t="n">
-        <v>159.257508289584</v>
+        <v>159.270048498166</v>
       </c>
     </row>
     <row r="146">
@@ -3365,7 +3365,7 @@
         <v>15</v>
       </c>
       <c r="F146" t="n">
-        <v>386.651697498182</v>
+        <v>386.651876869746</v>
       </c>
     </row>
     <row r="147">
@@ -3405,7 +3405,7 @@
         <v>15</v>
       </c>
       <c r="F148" t="n">
-        <v>92.6478632174243</v>
+        <v>92.6478468497724</v>
       </c>
     </row>
     <row r="149">
@@ -3465,7 +3465,7 @@
         <v>15</v>
       </c>
       <c r="F151" t="n">
-        <v>864.55613019401</v>
+        <v>864.557259669421</v>
       </c>
     </row>
     <row r="152">
@@ -3485,7 +3485,7 @@
         <v>15</v>
       </c>
       <c r="F152" t="n">
-        <v>432.665102790319</v>
+        <v>432.664804598456</v>
       </c>
     </row>
     <row r="153">
@@ -3505,7 +3505,7 @@
         <v>15</v>
       </c>
       <c r="F153" t="n">
-        <v>-390.880171333523</v>
+        <v>-390.807001904279</v>
       </c>
     </row>
     <row r="154">
@@ -3525,7 +3525,7 @@
         <v>15</v>
       </c>
       <c r="F154" t="n">
-        <v>155.522153671104</v>
+        <v>155.534752957642</v>
       </c>
     </row>
     <row r="155">
@@ -3545,7 +3545,7 @@
         <v>15</v>
       </c>
       <c r="F155" t="n">
-        <v>390.673822145371</v>
+        <v>390.674142334414</v>
       </c>
     </row>
     <row r="156">
@@ -3585,7 +3585,7 @@
         <v>15</v>
       </c>
       <c r="F157" t="n">
-        <v>88.6902110502673</v>
+        <v>88.6901986828222</v>
       </c>
     </row>
     <row r="158">
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="F158" t="n">
-        <v>549.024162646295</v>
+        <v>549.016614001295</v>
       </c>
     </row>
     <row r="159">
@@ -3645,7 +3645,7 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>865.991199575875</v>
+        <v>865.994331603001</v>
       </c>
     </row>
     <row r="161">
@@ -3665,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="F161" t="n">
-        <v>444.868146726001</v>
+        <v>444.867811887957</v>
       </c>
     </row>
     <row r="162">
@@ -3685,7 +3685,7 @@
         <v>15</v>
       </c>
       <c r="F162" t="n">
-        <v>-337.66301559224</v>
+        <v>-337.592402224959</v>
       </c>
     </row>
     <row r="163">
@@ -3705,7 +3705,7 @@
         <v>15</v>
       </c>
       <c r="F163" t="n">
-        <v>151.177135636189</v>
+        <v>151.189823820897</v>
       </c>
     </row>
     <row r="164">
@@ -3725,7 +3725,7 @@
         <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>386.672378972437</v>
+        <v>386.672976460796</v>
       </c>
     </row>
     <row r="165">
@@ -3785,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>529.30356335966</v>
+        <v>529.300466479659</v>
       </c>
     </row>
     <row r="168">
@@ -3825,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="F169" t="n">
-        <v>847.017914996818</v>
+        <v>847.022121728977</v>
       </c>
     </row>
     <row r="170">
@@ -3845,7 +3845,7 @@
         <v>15</v>
       </c>
       <c r="F170" t="n">
-        <v>419.760918513414</v>
+        <v>419.760656791329</v>
       </c>
     </row>
     <row r="171">
@@ -3865,7 +3865,7 @@
         <v>15</v>
       </c>
       <c r="F171" t="n">
-        <v>-386.3534333876</v>
+        <v>-386.291899153041</v>
       </c>
     </row>
     <row r="172">
@@ -3885,7 +3885,7 @@
         <v>15</v>
       </c>
       <c r="F172" t="n">
-        <v>147.037583527466</v>
+        <v>147.048018117946</v>
       </c>
     </row>
     <row r="173">
@@ -3905,7 +3905,7 @@
         <v>15</v>
       </c>
       <c r="F173" t="n">
-        <v>382.582341256757</v>
+        <v>382.583259080773</v>
       </c>
     </row>
     <row r="174">
@@ -3965,7 +3965,7 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>442.107561432475</v>
+        <v>442.102916112475</v>
       </c>
     </row>
     <row r="177">
@@ -4005,7 +4005,7 @@
         <v>15</v>
       </c>
       <c r="F178" t="n">
-        <v>825.406828726842</v>
+        <v>825.411957672594</v>
       </c>
     </row>
     <row r="179">
@@ -4025,7 +4025,7 @@
         <v>15</v>
       </c>
       <c r="F179" t="n">
-        <v>347.178183378787</v>
+        <v>347.178035163546</v>
       </c>
     </row>
     <row r="180">
@@ -4045,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="F180" t="n">
-        <v>-383.059868915005</v>
+        <v>-383.050536258084</v>
       </c>
     </row>
     <row r="181">
@@ -4065,7 +4065,7 @@
         <v>15</v>
       </c>
       <c r="F181" t="n">
-        <v>145.140964694808</v>
+        <v>145.151424872475</v>
       </c>
     </row>
     <row r="182">
@@ -4085,7 +4085,7 @@
         <v>15</v>
       </c>
       <c r="F182" t="n">
-        <v>378.968430250594</v>
+        <v>378.969557878834</v>
       </c>
     </row>
     <row r="183">
@@ -4145,7 +4145,7 @@
         <v>15</v>
       </c>
       <c r="F185" t="n">
-        <v>472.195564534162</v>
+        <v>472.186757781662</v>
       </c>
     </row>
     <row r="186">
@@ -4185,7 +4185,7 @@
         <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>819.562577513179</v>
+        <v>819.567875194593</v>
       </c>
     </row>
     <row r="188">
@@ -4205,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="F188" t="n">
-        <v>364.158260911068</v>
+        <v>364.158146460268</v>
       </c>
     </row>
     <row r="189">
@@ -4225,7 +4225,7 @@
         <v>15</v>
       </c>
       <c r="F189" t="n">
-        <v>-378.671770849729</v>
+        <v>-378.699121145596</v>
       </c>
     </row>
     <row r="190">
@@ -4245,7 +4245,7 @@
         <v>15</v>
       </c>
       <c r="F190" t="n">
-        <v>141.746392564725</v>
+        <v>141.757248078389</v>
       </c>
     </row>
     <row r="191">
@@ -4265,7 +4265,7 @@
         <v>15</v>
       </c>
       <c r="F191" t="n">
-        <v>375.680969136915</v>
+        <v>375.68270753027</v>
       </c>
     </row>
     <row r="192">
@@ -4325,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="F194" t="n">
-        <v>460.485116660447</v>
+        <v>460.477180905447</v>
       </c>
     </row>
     <row r="195">
@@ -4365,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>810.051154772734</v>
+        <v>810.056849237792</v>
       </c>
     </row>
     <row r="197">
@@ -4385,7 +4385,7 @@
         <v>15</v>
       </c>
       <c r="F197" t="n">
-        <v>363.939514530402</v>
+        <v>363.939435149798</v>
       </c>
     </row>
     <row r="198">
@@ -4405,7 +4405,7 @@
         <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>-363.100628818835</v>
+        <v>-363.073340661871</v>
       </c>
     </row>
     <row r="199">
@@ -4425,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="F199" t="n">
-        <v>137.293399656952</v>
+        <v>137.304294519526</v>
       </c>
     </row>
     <row r="200">
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="F200" t="n">
-        <v>374.752928289095</v>
+        <v>374.754373265413</v>
       </c>
     </row>
     <row r="201">
@@ -4505,7 +4505,7 @@
         <v>15</v>
       </c>
       <c r="F203" t="n">
-        <v>443.211935648427</v>
+        <v>443.205451555927</v>
       </c>
     </row>
     <row r="204">
@@ -4545,7 +4545,7 @@
         <v>15</v>
       </c>
       <c r="F205" t="n">
-        <v>780.485604968023</v>
+        <v>780.491256361539</v>
       </c>
     </row>
     <row r="206">
@@ -4565,7 +4565,7 @@
         <v>15</v>
       </c>
       <c r="F206" t="n">
-        <v>348.717542199638</v>
+        <v>348.717571029804</v>
       </c>
     </row>
     <row r="207">
@@ -4585,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="F207" t="n">
-        <v>-375.457106147434</v>
+        <v>-375.57198548376</v>
       </c>
     </row>
     <row r="208">
@@ -4605,7 +4605,7 @@
         <v>15</v>
       </c>
       <c r="F208" t="n">
-        <v>134.290174646277</v>
+        <v>134.301087748961</v>
       </c>
     </row>
     <row r="209">
@@ -4625,7 +4625,7 @@
         <v>15</v>
       </c>
       <c r="F209" t="n">
-        <v>378.475531834558</v>
+        <v>378.478357256499</v>
       </c>
     </row>
     <row r="210">
@@ -4685,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="F212" t="n">
-        <v>428.120218918589</v>
+        <v>428.111992831089</v>
       </c>
     </row>
     <row r="213">
@@ -4725,7 +4725,7 @@
         <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>774.35602601002</v>
+        <v>774.361553316007</v>
       </c>
     </row>
     <row r="215">
@@ -4745,7 +4745,7 @@
         <v>15</v>
       </c>
       <c r="F215" t="n">
-        <v>345.795573759698</v>
+        <v>345.795673719135</v>
       </c>
     </row>
     <row r="216">
@@ -4765,7 +4765,7 @@
         <v>15</v>
       </c>
       <c r="F216" t="n">
-        <v>-366.686103268182</v>
+        <v>-366.67263279599</v>
       </c>
     </row>
     <row r="217">
@@ -4785,7 +4785,7 @@
         <v>15</v>
       </c>
       <c r="F217" t="n">
-        <v>128.796508405893</v>
+        <v>128.795798173115</v>
       </c>
     </row>
     <row r="218">
@@ -4805,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="F218" t="n">
-        <v>382.8118820875</v>
+        <v>382.814684881579</v>
       </c>
     </row>
     <row r="219">
@@ -4865,7 +4865,7 @@
         <v>15</v>
       </c>
       <c r="F221" t="n">
-        <v>412.6366464112</v>
+        <v>412.6317164587</v>
       </c>
     </row>
     <row r="222">
@@ -4905,7 +4905,7 @@
         <v>15</v>
       </c>
       <c r="F223" t="n">
-        <v>780.205422330091</v>
+        <v>780.224017218109</v>
       </c>
     </row>
     <row r="224">
@@ -4925,7 +4925,7 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>352.750392368864</v>
+        <v>352.75061589119</v>
       </c>
     </row>
     <row r="225">
@@ -4945,7 +4945,7 @@
         <v>15</v>
       </c>
       <c r="F225" t="n">
-        <v>-342.791715313489</v>
+        <v>-342.821415950766</v>
       </c>
     </row>
     <row r="226">
@@ -4965,7 +4965,7 @@
         <v>15</v>
       </c>
       <c r="F226" t="n">
-        <v>124.817287743962</v>
+        <v>124.815980153406</v>
       </c>
     </row>
     <row r="227">
@@ -4985,7 +4985,7 @@
         <v>15</v>
       </c>
       <c r="F227" t="n">
-        <v>382.137407216639</v>
+        <v>382.140166524389</v>
       </c>
     </row>
     <row r="228">
@@ -5045,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>422.35926216855</v>
+        <v>422.35511213605</v>
       </c>
     </row>
     <row r="231">
@@ -5085,7 +5085,7 @@
         <v>15</v>
       </c>
       <c r="F232" t="n">
-        <v>795.756195977981</v>
+        <v>795.794808183666</v>
       </c>
     </row>
     <row r="233">
@@ -5105,7 +5105,7 @@
         <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>342.887843966889</v>
+        <v>342.888243486082</v>
       </c>
     </row>
     <row r="234">
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>-336.186559766275</v>
+        <v>-336.25602815955</v>
       </c>
     </row>
     <row r="235">
@@ -5145,7 +5145,7 @@
         <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>122.843468038302</v>
+        <v>122.846489907369</v>
       </c>
     </row>
     <row r="236">
@@ -5165,7 +5165,7 @@
         <v>15</v>
       </c>
       <c r="F236" t="n">
-        <v>385.79898732434</v>
+        <v>385.801739567362</v>
       </c>
     </row>
     <row r="237">
@@ -5225,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="F239" t="n">
-        <v>426.05530577665</v>
+        <v>426.04902663915</v>
       </c>
     </row>
     <row r="240">
@@ -5265,7 +5265,7 @@
         <v>15</v>
       </c>
       <c r="F241" t="n">
-        <v>813.383343727409</v>
+        <v>813.440837946639</v>
       </c>
     </row>
     <row r="242">
@@ -5285,7 +5285,7 @@
         <v>15</v>
       </c>
       <c r="F242" t="n">
-        <v>345.548171577652</v>
+        <v>345.548638359541</v>
       </c>
     </row>
     <row r="243">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="F243" t="n">
-        <v>-327.145621444847</v>
+        <v>-327.270670087944</v>
       </c>
     </row>
     <row r="244">
@@ -5325,7 +5325,7 @@
         <v>15</v>
       </c>
       <c r="F244" t="n">
-        <v>120.254687584334</v>
+        <v>120.247911090029</v>
       </c>
     </row>
     <row r="245">
@@ -5345,7 +5345,7 @@
         <v>15</v>
       </c>
       <c r="F245" t="n">
-        <v>386.999239380273</v>
+        <v>386.998983236156</v>
       </c>
     </row>
     <row r="246">
@@ -5405,7 +5405,7 @@
         <v>15</v>
       </c>
       <c r="F248" t="n">
-        <v>434.327341917065</v>
+        <v>434.327353317065</v>
       </c>
     </row>
     <row r="249">
@@ -5445,7 +5445,7 @@
         <v>15</v>
       </c>
       <c r="F250" t="n">
-        <v>828.146572989862</v>
+        <v>828.222401319256</v>
       </c>
     </row>
     <row r="251">
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="F251" t="n">
-        <v>351.997578863217</v>
+        <v>351.997979328137</v>
       </c>
     </row>
     <row r="252">
@@ -5485,7 +5485,7 @@
         <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>-271.843126590274</v>
+        <v>-272.273229813713</v>
       </c>
     </row>
     <row r="253">
@@ -5505,7 +5505,7 @@
         <v>15</v>
       </c>
       <c r="F253" t="n">
-        <v>119.231333072515</v>
+        <v>119.230301940475</v>
       </c>
     </row>
     <row r="254">
@@ -5525,7 +5525,7 @@
         <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>381.157510578263</v>
+        <v>381.157632828194</v>
       </c>
     </row>
     <row r="255">
@@ -5585,7 +5585,7 @@
         <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>434.570638284796</v>
+        <v>434.570664884796</v>
       </c>
     </row>
     <row r="258">
@@ -5625,7 +5625,7 @@
         <v>15</v>
       </c>
       <c r="F259" t="n">
-        <v>830.903660101338</v>
+        <v>830.996648000803</v>
       </c>
     </row>
     <row r="260">
@@ -5645,7 +5645,7 @@
         <v>15</v>
       </c>
       <c r="F260" t="n">
-        <v>344.983302531057</v>
+        <v>344.983814758336</v>
       </c>
     </row>
     <row r="261">
@@ -5665,7 +5665,7 @@
         <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>-239.324393665273</v>
+        <v>-239.537642139515</v>
       </c>
     </row>
     <row r="262">
@@ -5685,7 +5685,7 @@
         <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>117.967148064907</v>
+        <v>117.973465771897</v>
       </c>
     </row>
     <row r="263">
@@ -5705,7 +5705,7 @@
         <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>378.614518121346</v>
+        <v>378.61487830537</v>
       </c>
     </row>
     <row r="264">
@@ -5765,7 +5765,7 @@
         <v>15</v>
       </c>
       <c r="F266" t="n">
-        <v>423.739082988637</v>
+        <v>423.739119088637</v>
       </c>
     </row>
     <row r="267">
@@ -5805,7 +5805,7 @@
         <v>15</v>
       </c>
       <c r="F268" t="n">
-        <v>836.287786323883</v>
+        <v>836.396515751632</v>
       </c>
     </row>
     <row r="269">
@@ -5825,7 +5825,7 @@
         <v>15</v>
       </c>
       <c r="F269" t="n">
-        <v>331.778328277048</v>
+        <v>331.7785002785</v>
       </c>
     </row>
     <row r="270">
@@ -5845,7 +5845,7 @@
         <v>15</v>
       </c>
       <c r="F270" t="n">
-        <v>-233.803038618847</v>
+        <v>-234.049391240516</v>
       </c>
     </row>
     <row r="271">
@@ -5865,7 +5865,7 @@
         <v>15</v>
       </c>
       <c r="F271" t="n">
-        <v>117.097886308101</v>
+        <v>117.103656342323</v>
       </c>
     </row>
     <row r="272">
@@ -5885,7 +5885,7 @@
         <v>15</v>
       </c>
       <c r="F272" t="n">
-        <v>380.936076868425</v>
+        <v>380.936547946329</v>
       </c>
     </row>
     <row r="273">
@@ -5945,7 +5945,7 @@
         <v>15</v>
       </c>
       <c r="F275" t="n">
-        <v>403.198020838051</v>
+        <v>403.198055038051</v>
       </c>
     </row>
     <row r="276">
@@ -5985,7 +5985,7 @@
         <v>15</v>
       </c>
       <c r="F277" t="n">
-        <v>723.881520661935</v>
+        <v>723.974798965832</v>
       </c>
     </row>
     <row r="278">
@@ -6005,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="F278" t="n">
-        <v>307.000463074576</v>
+        <v>306.99700233498</v>
       </c>
     </row>
     <row r="279">
@@ -6025,7 +6025,7 @@
         <v>15</v>
       </c>
       <c r="F279" t="n">
-        <v>-237.439962869101</v>
+        <v>-237.404882686623</v>
       </c>
     </row>
     <row r="280">
@@ -6045,7 +6045,7 @@
         <v>15</v>
       </c>
       <c r="F280" t="n">
-        <v>116.565658631295</v>
+        <v>116.569928312921</v>
       </c>
     </row>
     <row r="281">
@@ -6065,7 +6065,7 @@
         <v>15</v>
       </c>
       <c r="F281" t="n">
-        <v>378.456442658931</v>
+        <v>378.45241946872</v>
       </c>
     </row>
     <row r="282">
@@ -6105,7 +6105,7 @@
         <v>15</v>
       </c>
       <c r="F283" t="n">
-        <v>54.0035470442178</v>
+        <v>53.9323295728326</v>
       </c>
     </row>
     <row r="284">
@@ -6125,7 +6125,7 @@
         <v>15</v>
       </c>
       <c r="F284" t="n">
-        <v>432.610561777493</v>
+        <v>432.610576977493</v>
       </c>
     </row>
     <row r="285">
@@ -6165,7 +6165,7 @@
         <v>15</v>
       </c>
       <c r="F286" t="n">
-        <v>785.177055609558</v>
+        <v>785.285184382794</v>
       </c>
     </row>
     <row r="287">
@@ -6185,7 +6185,7 @@
         <v>15</v>
       </c>
       <c r="F287" t="n">
-        <v>317.36450825643</v>
+        <v>317.147415286101</v>
       </c>
     </row>
     <row r="288">
@@ -6205,7 +6205,7 @@
         <v>15</v>
       </c>
       <c r="F288" t="n">
-        <v>-225.631263537836</v>
+        <v>-225.689718540378</v>
       </c>
     </row>
     <row r="289">
@@ -6225,7 +6225,7 @@
         <v>15</v>
       </c>
       <c r="F289" t="n">
-        <v>115.378268416337</v>
+        <v>115.384684146544</v>
       </c>
     </row>
     <row r="290">
@@ -6245,7 +6245,7 @@
         <v>15</v>
       </c>
       <c r="F290" t="n">
-        <v>364.65677975327</v>
+        <v>364.652844399226</v>
       </c>
     </row>
     <row r="291">
@@ -6265,7 +6265,7 @@
         <v>15</v>
       </c>
       <c r="F291" t="n">
-        <v>476.648726158465</v>
+        <v>476.648715781798</v>
       </c>
     </row>
     <row r="292">
@@ -6305,7 +6305,7 @@
         <v>15</v>
       </c>
       <c r="F293" t="n">
-        <v>394.458487720157</v>
+        <v>394.456367149157</v>
       </c>
     </row>
     <row r="294">
@@ -6345,7 +6345,7 @@
         <v>15</v>
       </c>
       <c r="F295" t="n">
-        <v>806.245050946072</v>
+        <v>806.357177848384</v>
       </c>
     </row>
     <row r="296">
@@ -6365,7 +6365,7 @@
         <v>15</v>
       </c>
       <c r="F296" t="n">
-        <v>290.866075172269</v>
+        <v>290.655098865058</v>
       </c>
     </row>
     <row r="297">
@@ -6385,7 +6385,7 @@
         <v>15</v>
       </c>
       <c r="F297" t="n">
-        <v>-220.559672255561</v>
+        <v>-218.900833648047</v>
       </c>
     </row>
     <row r="298">
@@ -6405,7 +6405,7 @@
         <v>15</v>
       </c>
       <c r="F298" t="n">
-        <v>114.280342861803</v>
+        <v>114.288551962458</v>
       </c>
     </row>
     <row r="299">
@@ -6425,7 +6425,7 @@
         <v>15</v>
       </c>
       <c r="F299" t="n">
-        <v>363.619563591554</v>
+        <v>363.634995714859</v>
       </c>
     </row>
     <row r="300">
@@ -6465,7 +6465,7 @@
         <v>15</v>
       </c>
       <c r="F301" t="n">
-        <v>47.89283934417</v>
+        <v>47.8906554987224</v>
       </c>
     </row>
     <row r="302">
@@ -6485,7 +6485,7 @@
         <v>15</v>
       </c>
       <c r="F302" t="n">
-        <v>362.417138597088</v>
+        <v>362.425065027088</v>
       </c>
     </row>
     <row r="303">
@@ -6505,7 +6505,7 @@
         <v>15</v>
       </c>
       <c r="F303" t="n">
-        <v>699.37918405304</v>
+        <v>699.367960891016</v>
       </c>
     </row>
     <row r="304">
@@ -6525,7 +6525,7 @@
         <v>15</v>
       </c>
       <c r="F304" t="n">
-        <v>797.146235086097</v>
+        <v>797.242542334988</v>
       </c>
     </row>
     <row r="305">
@@ -6545,7 +6545,7 @@
         <v>15</v>
       </c>
       <c r="F305" t="n">
-        <v>264.715418515633</v>
+        <v>264.528695162379</v>
       </c>
     </row>
     <row r="306">
@@ -6565,7 +6565,7 @@
         <v>15</v>
       </c>
       <c r="F306" t="n">
-        <v>-215.366950497865</v>
+        <v>-214.915850472983</v>
       </c>
     </row>
     <row r="307">
@@ -6585,7 +6585,7 @@
         <v>15</v>
       </c>
       <c r="F307" t="n">
-        <v>113.204799545644</v>
+        <v>113.212840843608</v>
       </c>
     </row>
     <row r="308">
@@ -6605,7 +6605,7 @@
         <v>15</v>
       </c>
       <c r="F308" t="n">
-        <v>353.177513845974</v>
+        <v>359.482059777194</v>
       </c>
     </row>
     <row r="309">
@@ -6625,7 +6625,7 @@
         <v>15</v>
       </c>
       <c r="F309" t="n">
-        <v>428.822980211391</v>
+        <v>438.67061671554</v>
       </c>
     </row>
     <row r="310">
@@ -6645,7 +6645,7 @@
         <v>15</v>
       </c>
       <c r="F310" t="n">
-        <v>45.3381911005699</v>
+        <v>46.7121104696898</v>
       </c>
     </row>
     <row r="311">
@@ -6665,7 +6665,7 @@
         <v>15</v>
       </c>
       <c r="F311" t="n">
-        <v>349.219056656656</v>
+        <v>353.298760073858</v>
       </c>
     </row>
     <row r="312">
@@ -6685,7 +6685,7 @@
         <v>15</v>
       </c>
       <c r="F312" t="n">
-        <v>634.595728653527</v>
+        <v>643.318111399857</v>
       </c>
     </row>
     <row r="313">
@@ -6705,7 +6705,7 @@
         <v>15</v>
       </c>
       <c r="F313" t="n">
-        <v>792.215181953101</v>
+        <v>806.231398260337</v>
       </c>
     </row>
     <row r="314">
@@ -6725,7 +6725,7 @@
         <v>15</v>
       </c>
       <c r="F314" t="n">
-        <v>255.296238997502</v>
+        <v>260.607584542628</v>
       </c>
     </row>
     <row r="315">
@@ -6745,7 +6745,7 @@
         <v>15</v>
       </c>
       <c r="F315" t="n">
-        <v>-223.952189656652</v>
+        <v>-230.292584574363</v>
       </c>
     </row>
     <row r="316">
@@ -6765,7 +6765,7 @@
         <v>15</v>
       </c>
       <c r="F316" t="n">
-        <v>107.802659258882</v>
+        <v>111.806023580071</v>
       </c>
     </row>
   </sheetData>
